--- a/docs/Carwash_QA_Testing_Document.xlsx
+++ b/docs/Carwash_QA_Testing_Document.xlsx
@@ -1,26 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ricky\Documents\KULIAH\CAPSTONEPROJECT\Carwash-IoT-System\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661E5A31-3E3E-44B4-8B36-8C96B7394BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="5" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Scenario" sheetId="1" r:id="rId4"/>
-    <sheet name="Test Case" sheetId="2" r:id="rId5"/>
-    <sheet name="Test Data" sheetId="3" r:id="rId6"/>
-    <sheet name="Bug" sheetId="4" r:id="rId7"/>
-    <sheet name="Test Report" sheetId="5" r:id="rId8"/>
-    <sheet name="Task" sheetId="6" r:id="rId9"/>
+    <sheet name="Test Scenario" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Case" sheetId="2" r:id="rId2"/>
+    <sheet name="Test Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Bug" sheetId="4" r:id="rId4"/>
+    <sheet name="Test Report" sheetId="5" r:id="rId5"/>
+    <sheet name="Task" sheetId="6" r:id="rId6"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="430">
   <si>
     <t>Project Name</t>
   </si>
@@ -1385,84 +1401,64 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="single"/>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF173B72"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF173B72"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1527,6 +1523,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1752,196 +1760,227 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+  <cellXfs count="77">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="14" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="6" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="6" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="17" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="14" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="14" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="10" fontId="4" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="10" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="17" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="17" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="14" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="8" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="9" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="14" fillId="0" borderId="6" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="10" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="11" borderId="16" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="14" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="14" fillId="6" borderId="6" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="8" borderId="15" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="9" fillId="6" borderId="17" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="10" fillId="6" borderId="6" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="4" numFmtId="10" fillId="6" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="10" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="10" fillId="2" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="10" fillId="0" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="9" fillId="0" borderId="6" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="9" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" quotePrefix="1" numFmtId="9" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="10" fillId="0" borderId="6" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="5" numFmtId="14" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="6" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2265,26 +2304,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31" customWidth="true" style="1"/>
-    <col min="2" max="2" width="55.33203125" customWidth="true" style="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="true" style="1"/>
-    <col min="4" max="4" width="4.88671875" customWidth="true" style="1"/>
-    <col min="5" max="5" width="20.21875" customWidth="true" style="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="true" style="1"/>
-    <col min="7" max="7" width="29.109375" customWidth="true" style="1"/>
-    <col min="8" max="8" width="37.44140625" customWidth="true" style="1"/>
-    <col min="9" max="9" width="8.88671875" customWidth="true" style="1"/>
+    <col min="1" max="1" width="31" style="1" customWidth="1"/>
+    <col min="2" max="2" width="55.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2309,7 +2347,7 @@
       </c>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:9" customHeight="1" ht="28.8">
+    <row r="2" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -2334,7 +2372,7 @@
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" customHeight="1" ht="28.8">
+    <row r="3" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -2359,7 +2397,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" customHeight="1" ht="28.8">
+    <row r="4" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2380,7 +2418,7 @@
       </c>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" customHeight="1" ht="28.8">
+    <row r="5" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2401,7 +2439,7 @@
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -2422,7 +2460,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2443,7 +2481,7 @@
       </c>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2464,7 +2502,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2485,7 +2523,7 @@
       </c>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2506,7 +2544,7 @@
       </c>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2517,7 +2555,7 @@
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2528,7 +2566,7 @@
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -2539,7 +2577,7 @@
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2550,7 +2588,7 @@
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -2561,7 +2599,7 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -2572,7 +2610,7 @@
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -2583,7 +2621,7 @@
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2594,7 +2632,7 @@
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -2605,7 +2643,7 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2616,7 +2654,7 @@
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2627,7 +2665,7 @@
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2638,7 +2676,7 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2649,7 +2687,7 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -2660,7 +2698,7 @@
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2671,7 +2709,7 @@
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2682,7 +2720,7 @@
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2693,7 +2731,7 @@
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2704,7 +2742,7 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2715,7 +2753,7 @@
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2727,187 +2765,174 @@
       <c r="I30" s="5"/>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:N140"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="true" style="1"/>
-    <col min="2" max="2" width="14" customWidth="true" style="1"/>
-    <col min="3" max="3" width="22" customWidth="true" style="1"/>
-    <col min="4" max="4" width="16" customWidth="true" style="1"/>
-    <col min="5" max="5" width="14" customWidth="true" style="1"/>
-    <col min="6" max="6" width="32" customWidth="true" style="1"/>
-    <col min="7" max="7" width="28" customWidth="true" style="1"/>
-    <col min="8" max="8" width="42" customWidth="true" style="1"/>
-    <col min="9" max="9" width="42" customWidth="true" style="1"/>
-    <col min="10" max="10" width="12" customWidth="true" style="1"/>
-    <col min="11" max="11" width="11" customWidth="true" style="1"/>
-    <col min="12" max="12" width="15" customWidth="true" style="1"/>
-    <col min="13" max="13" width="24" customWidth="true" style="1"/>
-    <col min="14" max="14" width="8.88671875" customWidth="true" style="1"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28" style="1" customWidth="1"/>
+    <col min="8" max="9" width="42" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="12" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
       <c r="N1" s="5"/>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="17" t="s">
+      <c r="B2" s="66"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
       <c r="N2" s="5"/>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="69"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
       <c r="N3" s="5"/>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="28" t="s">
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30" t="s">
+      <c r="E4" s="73"/>
+      <c r="F4" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="J4" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
       <c r="N4" s="5"/>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="28">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="71"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="72">
         <f>COUNTIF(J8:J62,"Passed")</f>
         <v>0</v>
       </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30">
+      <c r="E5" s="73"/>
+      <c r="F5" s="17">
         <f>COUNTIF(J8:J62,"Fail")</f>
         <v>0</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="17">
         <f>COUNTIF(J8:J62,"Pending")</f>
         <v>55</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="19">
         <f>COUNTIF(J8:J62,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="19">
         <f>COUNTIF(J8:J62,"Invalid")</f>
         <v>0</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="74">
         <f>COUNTA(D8:D62)</f>
         <v>55</v>
       </c>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="20"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:14" customHeight="1" ht="27.6">
+    <row r="7" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>50</v>
       </c>
@@ -2947,9 +2972,9 @@
       <c r="M7" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="N7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" customHeight="1" ht="64">
+      <c r="N7" s="13"/>
+    </row>
+    <row r="8" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -2965,7 +2990,7 @@
       <c r="E8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="55" t="s">
         <v>65</v>
       </c>
       <c r="G8" s="4" t="s">
@@ -2987,9 +3012,9 @@
         <v>69</v>
       </c>
       <c r="M8" s="4"/>
-      <c r="N8" s="15"/>
-    </row>
-    <row r="9" spans="1:14" customHeight="1" ht="64">
+      <c r="N8" s="13"/>
+    </row>
+    <row r="9" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
@@ -3005,7 +3030,7 @@
       <c r="E9" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="55" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="4" t="s">
@@ -3027,9 +3052,9 @@
         <v>69</v>
       </c>
       <c r="M9" s="4"/>
-      <c r="N9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" customHeight="1" ht="64">
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -3045,7 +3070,7 @@
       <c r="E10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="55" t="s">
         <v>76</v>
       </c>
       <c r="G10" s="4" t="s">
@@ -3067,9 +3092,9 @@
         <v>69</v>
       </c>
       <c r="M10" s="4"/>
-      <c r="N10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" customHeight="1" ht="64">
+      <c r="N10" s="13"/>
+    </row>
+    <row r="11" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -3085,7 +3110,7 @@
       <c r="E11" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="55" t="s">
         <v>82</v>
       </c>
       <c r="G11" s="4" t="s">
@@ -3107,9 +3132,9 @@
         <v>69</v>
       </c>
       <c r="M11" s="4"/>
-      <c r="N11" s="15"/>
-    </row>
-    <row r="12" spans="1:14" customHeight="1" ht="64">
+      <c r="N11" s="13"/>
+    </row>
+    <row r="12" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
@@ -3125,7 +3150,7 @@
       <c r="E12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="55" t="s">
         <v>87</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -3147,9 +3172,9 @@
         <v>69</v>
       </c>
       <c r="M12" s="4"/>
-      <c r="N12" s="15"/>
-    </row>
-    <row r="13" spans="1:14" customHeight="1" ht="64">
+      <c r="N12" s="13"/>
+    </row>
+    <row r="13" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
@@ -3165,7 +3190,7 @@
       <c r="E13" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="55" t="s">
         <v>91</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -3187,9 +3212,9 @@
         <v>69</v>
       </c>
       <c r="M13" s="4"/>
-      <c r="N13" s="15"/>
-    </row>
-    <row r="14" spans="1:14" customHeight="1" ht="64">
+      <c r="N13" s="13"/>
+    </row>
+    <row r="14" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>9</v>
       </c>
@@ -3205,7 +3230,7 @@
       <c r="E14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="55" t="s">
         <v>96</v>
       </c>
       <c r="G14" s="4" t="s">
@@ -3227,9 +3252,9 @@
         <v>69</v>
       </c>
       <c r="M14" s="4"/>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:14" customHeight="1" ht="64">
+      <c r="N14" s="13"/>
+    </row>
+    <row r="15" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
@@ -3267,9 +3292,9 @@
         <v>69</v>
       </c>
       <c r="M15" s="4"/>
-      <c r="N15" s="15"/>
-    </row>
-    <row r="16" spans="1:14" customHeight="1" ht="64">
+      <c r="N15" s="13"/>
+    </row>
+    <row r="16" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
@@ -3285,7 +3310,7 @@
       <c r="E16" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="55" t="s">
         <v>106</v>
       </c>
       <c r="G16" s="4" t="s">
@@ -3307,9 +3332,9 @@
         <v>69</v>
       </c>
       <c r="M16" s="4"/>
-      <c r="N16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" customHeight="1" ht="64">
+      <c r="N16" s="13"/>
+    </row>
+    <row r="17" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>14</v>
       </c>
@@ -3347,9 +3372,9 @@
         <v>69</v>
       </c>
       <c r="M17" s="4"/>
-      <c r="N17" s="15"/>
-    </row>
-    <row r="18" spans="1:14" customHeight="1" ht="64">
+      <c r="N17" s="13"/>
+    </row>
+    <row r="18" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
@@ -3365,7 +3390,7 @@
       <c r="E18" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="55" t="s">
         <v>116</v>
       </c>
       <c r="G18" s="4" t="s">
@@ -3387,9 +3412,9 @@
         <v>69</v>
       </c>
       <c r="M18" s="4"/>
-      <c r="N18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" customHeight="1" ht="64">
+      <c r="N18" s="13"/>
+    </row>
+    <row r="19" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
@@ -3427,9 +3452,9 @@
         <v>69</v>
       </c>
       <c r="M19" s="4"/>
-      <c r="N19" s="15"/>
-    </row>
-    <row r="20" spans="1:14" customHeight="1" ht="64">
+      <c r="N19" s="13"/>
+    </row>
+    <row r="20" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>14</v>
       </c>
@@ -3467,9 +3492,9 @@
         <v>129</v>
       </c>
       <c r="M20" s="4"/>
-      <c r="N20" s="15"/>
-    </row>
-    <row r="21" spans="1:14" customHeight="1" ht="64">
+      <c r="N20" s="13"/>
+    </row>
+    <row r="21" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>17</v>
       </c>
@@ -3485,7 +3510,7 @@
       <c r="E21" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="55" t="s">
         <v>131</v>
       </c>
       <c r="G21" s="4" t="s">
@@ -3507,9 +3532,9 @@
         <v>69</v>
       </c>
       <c r="M21" s="4"/>
-      <c r="N21" s="15"/>
-    </row>
-    <row r="22" spans="1:14" customHeight="1" ht="64">
+      <c r="N21" s="13"/>
+    </row>
+    <row r="22" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
@@ -3525,7 +3550,7 @@
       <c r="E22" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="55" t="s">
         <v>136</v>
       </c>
       <c r="G22" s="4" t="s">
@@ -3547,9 +3572,9 @@
         <v>69</v>
       </c>
       <c r="M22" s="4"/>
-      <c r="N22" s="15"/>
-    </row>
-    <row r="23" spans="1:14" customHeight="1" ht="64">
+      <c r="N22" s="13"/>
+    </row>
+    <row r="23" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
@@ -3587,9 +3612,9 @@
         <v>129</v>
       </c>
       <c r="M23" s="4"/>
-      <c r="N23" s="15"/>
-    </row>
-    <row r="24" spans="1:14" customHeight="1" ht="64">
+      <c r="N23" s="13"/>
+    </row>
+    <row r="24" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>17</v>
       </c>
@@ -3627,9 +3652,9 @@
         <v>150</v>
       </c>
       <c r="M24" s="4"/>
-      <c r="N24" s="15"/>
-    </row>
-    <row r="25" spans="1:14" customHeight="1" ht="64">
+      <c r="N24" s="13"/>
+    </row>
+    <row r="25" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>17</v>
       </c>
@@ -3667,9 +3692,9 @@
         <v>150</v>
       </c>
       <c r="M25" s="4"/>
-      <c r="N25" s="15"/>
-    </row>
-    <row r="26" spans="1:14" customHeight="1" ht="64">
+      <c r="N25" s="13"/>
+    </row>
+    <row r="26" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>20</v>
       </c>
@@ -3685,7 +3710,7 @@
       <c r="E26" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="55" t="s">
         <v>157</v>
       </c>
       <c r="G26" s="4" t="s">
@@ -3707,9 +3732,9 @@
         <v>69</v>
       </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="15"/>
-    </row>
-    <row r="27" spans="1:14" customHeight="1" ht="64">
+      <c r="N26" s="13"/>
+    </row>
+    <row r="27" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>20</v>
       </c>
@@ -3725,7 +3750,7 @@
       <c r="E27" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="55" t="s">
         <v>162</v>
       </c>
       <c r="G27" s="4" t="s">
@@ -3747,9 +3772,9 @@
         <v>69</v>
       </c>
       <c r="M27" s="4"/>
-      <c r="N27" s="15"/>
-    </row>
-    <row r="28" spans="1:14" customHeight="1" ht="64">
+      <c r="N27" s="13"/>
+    </row>
+    <row r="28" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>20</v>
       </c>
@@ -3765,7 +3790,7 @@
       <c r="E28" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="55" t="s">
         <v>167</v>
       </c>
       <c r="G28" s="4" t="s">
@@ -3787,9 +3812,9 @@
         <v>69</v>
       </c>
       <c r="M28" s="4"/>
-      <c r="N28" s="15"/>
-    </row>
-    <row r="29" spans="1:14" customHeight="1" ht="64">
+      <c r="N28" s="13"/>
+    </row>
+    <row r="29" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>20</v>
       </c>
@@ -3827,9 +3852,9 @@
         <v>69</v>
       </c>
       <c r="M29" s="4"/>
-      <c r="N29" s="15"/>
-    </row>
-    <row r="30" spans="1:14" customHeight="1" ht="64">
+      <c r="N29" s="13"/>
+    </row>
+    <row r="30" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -3845,7 +3870,7 @@
       <c r="E30" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="56" t="s">
         <v>175</v>
       </c>
       <c r="G30" s="4" t="s">
@@ -3867,9 +3892,9 @@
         <v>69</v>
       </c>
       <c r="M30" s="4"/>
-      <c r="N30" s="15"/>
-    </row>
-    <row r="31" spans="1:14" customHeight="1" ht="64">
+      <c r="N30" s="13"/>
+    </row>
+    <row r="31" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>20</v>
       </c>
@@ -3885,7 +3910,7 @@
       <c r="E31" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="55" t="s">
         <v>180</v>
       </c>
       <c r="G31" s="4" t="s">
@@ -3907,9 +3932,9 @@
         <v>184</v>
       </c>
       <c r="M31" s="4"/>
-      <c r="N31" s="15"/>
-    </row>
-    <row r="32" spans="1:14" customHeight="1" ht="64">
+      <c r="N31" s="13"/>
+    </row>
+    <row r="32" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>23</v>
       </c>
@@ -3925,7 +3950,7 @@
       <c r="E32" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="55" t="s">
         <v>186</v>
       </c>
       <c r="G32" s="4" t="s">
@@ -3934,7 +3959,7 @@
       <c r="H32" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="I32" s="12" t="s">
         <v>189</v>
       </c>
       <c r="J32" s="4" t="s">
@@ -3947,9 +3972,9 @@
         <v>69</v>
       </c>
       <c r="M32" s="4"/>
-      <c r="N32" s="15"/>
-    </row>
-    <row r="33" spans="1:14" customHeight="1" ht="64">
+      <c r="N32" s="13"/>
+    </row>
+    <row r="33" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>23</v>
       </c>
@@ -3965,7 +3990,7 @@
       <c r="E33" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="55" t="s">
         <v>191</v>
       </c>
       <c r="G33" s="4" t="s">
@@ -3987,9 +4012,9 @@
         <v>69</v>
       </c>
       <c r="M33" s="4"/>
-      <c r="N33" s="15"/>
-    </row>
-    <row r="34" spans="1:14" customHeight="1" ht="64">
+      <c r="N33" s="13"/>
+    </row>
+    <row r="34" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>23</v>
       </c>
@@ -4005,7 +4030,7 @@
       <c r="E34" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="55" t="s">
         <v>196</v>
       </c>
       <c r="G34" s="4" t="s">
@@ -4027,9 +4052,9 @@
         <v>69</v>
       </c>
       <c r="M34" s="4"/>
-      <c r="N34" s="15"/>
-    </row>
-    <row r="35" spans="1:14" customHeight="1" ht="64">
+      <c r="N34" s="13"/>
+    </row>
+    <row r="35" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>23</v>
       </c>
@@ -4045,7 +4070,7 @@
       <c r="E35" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="55" t="s">
         <v>200</v>
       </c>
       <c r="G35" s="4" t="s">
@@ -4067,9 +4092,9 @@
         <v>69</v>
       </c>
       <c r="M35" s="4"/>
-      <c r="N35" s="15"/>
-    </row>
-    <row r="36" spans="1:14" customHeight="1" ht="64">
+      <c r="N35" s="13"/>
+    </row>
+    <row r="36" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>23</v>
       </c>
@@ -4085,7 +4110,7 @@
       <c r="E36" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="55" t="s">
         <v>205</v>
       </c>
       <c r="G36" s="4" t="s">
@@ -4107,9 +4132,9 @@
         <v>69</v>
       </c>
       <c r="M36" s="4"/>
-      <c r="N36" s="15"/>
-    </row>
-    <row r="37" spans="1:14" customHeight="1" ht="64">
+      <c r="N36" s="13"/>
+    </row>
+    <row r="37" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>23</v>
       </c>
@@ -4125,7 +4150,7 @@
       <c r="E37" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="55" t="s">
         <v>209</v>
       </c>
       <c r="G37" s="4" t="s">
@@ -4147,9 +4172,9 @@
         <v>69</v>
       </c>
       <c r="M37" s="4"/>
-      <c r="N37" s="15"/>
-    </row>
-    <row r="38" spans="1:14" customHeight="1" ht="64">
+      <c r="N37" s="13"/>
+    </row>
+    <row r="38" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>26</v>
       </c>
@@ -4165,7 +4190,7 @@
       <c r="E38" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="56" t="s">
         <v>213</v>
       </c>
       <c r="G38" s="4" t="s">
@@ -4187,9 +4212,9 @@
         <v>69</v>
       </c>
       <c r="M38" s="4"/>
-      <c r="N38" s="15"/>
-    </row>
-    <row r="39" spans="1:14" customHeight="1" ht="64">
+      <c r="N38" s="13"/>
+    </row>
+    <row r="39" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>26</v>
       </c>
@@ -4205,7 +4230,7 @@
       <c r="E39" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="56" t="s">
         <v>218</v>
       </c>
       <c r="G39" s="4" t="s">
@@ -4227,9 +4252,9 @@
         <v>69</v>
       </c>
       <c r="M39" s="4"/>
-      <c r="N39" s="15"/>
-    </row>
-    <row r="40" spans="1:14" customHeight="1" ht="64">
+      <c r="N39" s="13"/>
+    </row>
+    <row r="40" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>26</v>
       </c>
@@ -4245,7 +4270,7 @@
       <c r="E40" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="55" t="s">
         <v>222</v>
       </c>
       <c r="G40" s="4" t="s">
@@ -4267,9 +4292,9 @@
         <v>69</v>
       </c>
       <c r="M40" s="4"/>
-      <c r="N40" s="15"/>
-    </row>
-    <row r="41" spans="1:14" customHeight="1" ht="64">
+      <c r="N40" s="13"/>
+    </row>
+    <row r="41" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>26</v>
       </c>
@@ -4285,7 +4310,7 @@
       <c r="E41" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="55" t="s">
         <v>227</v>
       </c>
       <c r="G41" s="4" t="s">
@@ -4307,9 +4332,9 @@
         <v>69</v>
       </c>
       <c r="M41" s="4"/>
-      <c r="N41" s="15"/>
-    </row>
-    <row r="42" spans="1:14" customHeight="1" ht="64">
+      <c r="N41" s="13"/>
+    </row>
+    <row r="42" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>26</v>
       </c>
@@ -4325,7 +4350,7 @@
       <c r="E42" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="56" t="s">
         <v>232</v>
       </c>
       <c r="G42" s="4" t="s">
@@ -4347,9 +4372,9 @@
         <v>69</v>
       </c>
       <c r="M42" s="4"/>
-      <c r="N42" s="15"/>
-    </row>
-    <row r="43" spans="1:14" customHeight="1" ht="64">
+      <c r="N42" s="13"/>
+    </row>
+    <row r="43" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>26</v>
       </c>
@@ -4365,7 +4390,7 @@
       <c r="E43" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="55" t="s">
         <v>236</v>
       </c>
       <c r="G43" s="4" t="s">
@@ -4387,9 +4412,9 @@
         <v>69</v>
       </c>
       <c r="M43" s="4"/>
-      <c r="N43" s="15"/>
-    </row>
-    <row r="44" spans="1:14" customHeight="1" ht="64">
+      <c r="N43" s="13"/>
+    </row>
+    <row r="44" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>26</v>
       </c>
@@ -4405,7 +4430,7 @@
       <c r="E44" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="55" t="s">
         <v>240</v>
       </c>
       <c r="G44" s="4" t="s">
@@ -4427,9 +4452,9 @@
         <v>69</v>
       </c>
       <c r="M44" s="4"/>
-      <c r="N44" s="15"/>
-    </row>
-    <row r="45" spans="1:14" customHeight="1" ht="64">
+      <c r="N44" s="13"/>
+    </row>
+    <row r="45" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>29</v>
       </c>
@@ -4445,7 +4470,7 @@
       <c r="E45" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="55" t="s">
         <v>245</v>
       </c>
       <c r="G45" s="4" t="s">
@@ -4467,9 +4492,9 @@
         <v>69</v>
       </c>
       <c r="M45" s="4"/>
-      <c r="N45" s="15"/>
-    </row>
-    <row r="46" spans="1:14" customHeight="1" ht="64">
+      <c r="N45" s="13"/>
+    </row>
+    <row r="46" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>29</v>
       </c>
@@ -4485,7 +4510,7 @@
       <c r="E46" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="55" t="s">
         <v>249</v>
       </c>
       <c r="G46" s="4" t="s">
@@ -4507,9 +4532,9 @@
         <v>69</v>
       </c>
       <c r="M46" s="4"/>
-      <c r="N46" s="15"/>
-    </row>
-    <row r="47" spans="1:14" customHeight="1" ht="64">
+      <c r="N46" s="13"/>
+    </row>
+    <row r="47" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>29</v>
       </c>
@@ -4525,7 +4550,7 @@
       <c r="E47" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="55" t="s">
         <v>254</v>
       </c>
       <c r="G47" s="4" t="s">
@@ -4547,9 +4572,9 @@
         <v>69</v>
       </c>
       <c r="M47" s="4"/>
-      <c r="N47" s="15"/>
-    </row>
-    <row r="48" spans="1:14" customHeight="1" ht="64">
+      <c r="N47" s="13"/>
+    </row>
+    <row r="48" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>29</v>
       </c>
@@ -4565,7 +4590,7 @@
       <c r="E48" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="55" t="s">
         <v>259</v>
       </c>
       <c r="G48" s="4" t="s">
@@ -4587,9 +4612,9 @@
         <v>69</v>
       </c>
       <c r="M48" s="4"/>
-      <c r="N48" s="15"/>
-    </row>
-    <row r="49" spans="1:14" customHeight="1" ht="64">
+      <c r="N48" s="13"/>
+    </row>
+    <row r="49" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>29</v>
       </c>
@@ -4605,7 +4630,7 @@
       <c r="E49" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="56" t="s">
         <v>262</v>
       </c>
       <c r="G49" s="4" t="s">
@@ -4627,9 +4652,9 @@
         <v>69</v>
       </c>
       <c r="M49" s="4"/>
-      <c r="N49" s="15"/>
-    </row>
-    <row r="50" spans="1:14" customHeight="1" ht="64">
+      <c r="N49" s="13"/>
+    </row>
+    <row r="50" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>29</v>
       </c>
@@ -4645,7 +4670,7 @@
       <c r="E50" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="55" t="s">
         <v>266</v>
       </c>
       <c r="G50" s="4" t="s">
@@ -4669,7 +4694,7 @@
       <c r="M50" s="4"/>
       <c r="N50" s="5"/>
     </row>
-    <row r="51" spans="1:14" customHeight="1" ht="64">
+    <row r="51" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>32</v>
       </c>
@@ -4685,7 +4710,7 @@
       <c r="E51" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="55" t="s">
         <v>269</v>
       </c>
       <c r="G51" s="4" t="s">
@@ -4709,7 +4734,7 @@
       <c r="M51" s="4"/>
       <c r="N51" s="5"/>
     </row>
-    <row r="52" spans="1:14" customHeight="1" ht="64">
+    <row r="52" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>32</v>
       </c>
@@ -4725,7 +4750,7 @@
       <c r="E52" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="55" t="s">
         <v>274</v>
       </c>
       <c r="G52" s="4" t="s">
@@ -4749,7 +4774,7 @@
       <c r="M52" s="4"/>
       <c r="N52" s="5"/>
     </row>
-    <row r="53" spans="1:14" customHeight="1" ht="64">
+    <row r="53" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>32</v>
       </c>
@@ -4765,7 +4790,7 @@
       <c r="E53" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="55" t="s">
         <v>279</v>
       </c>
       <c r="G53" s="4" t="s">
@@ -4789,7 +4814,7 @@
       <c r="M53" s="4"/>
       <c r="N53" s="5"/>
     </row>
-    <row r="54" spans="1:14" customHeight="1" ht="64">
+    <row r="54" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>32</v>
       </c>
@@ -4805,7 +4830,7 @@
       <c r="E54" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="55" t="s">
         <v>284</v>
       </c>
       <c r="G54" s="4" t="s">
@@ -4829,7 +4854,7 @@
       <c r="M54" s="4"/>
       <c r="N54" s="5"/>
     </row>
-    <row r="55" spans="1:14" customHeight="1" ht="64">
+    <row r="55" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>35</v>
       </c>
@@ -4845,7 +4870,7 @@
       <c r="E55" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="55" t="s">
         <v>287</v>
       </c>
       <c r="G55" s="4" t="s">
@@ -4869,7 +4894,7 @@
       <c r="M55" s="4"/>
       <c r="N55" s="5"/>
     </row>
-    <row r="56" spans="1:14" customHeight="1" ht="64">
+    <row r="56" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>35</v>
       </c>
@@ -4885,7 +4910,7 @@
       <c r="E56" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="55" t="s">
         <v>292</v>
       </c>
       <c r="G56" s="4" t="s">
@@ -4909,7 +4934,7 @@
       <c r="M56" s="4"/>
       <c r="N56" s="5"/>
     </row>
-    <row r="57" spans="1:14" customHeight="1" ht="64">
+    <row r="57" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>35</v>
       </c>
@@ -4949,7 +4974,7 @@
       <c r="M57" s="4"/>
       <c r="N57" s="5"/>
     </row>
-    <row r="58" spans="1:14" customHeight="1" ht="64">
+    <row r="58" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>35</v>
       </c>
@@ -4989,7 +5014,7 @@
       <c r="M58" s="4"/>
       <c r="N58" s="5"/>
     </row>
-    <row r="59" spans="1:14" customHeight="1" ht="64">
+    <row r="59" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>35</v>
       </c>
@@ -5029,7 +5054,7 @@
       <c r="M59" s="4"/>
       <c r="N59" s="5"/>
     </row>
-    <row r="60" spans="1:14" customHeight="1" ht="64">
+    <row r="60" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>35</v>
       </c>
@@ -5069,7 +5094,7 @@
       <c r="M60" s="4"/>
       <c r="N60" s="5"/>
     </row>
-    <row r="61" spans="1:14" customHeight="1" ht="64">
+    <row r="61" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>35</v>
       </c>
@@ -5109,7 +5134,7 @@
       <c r="M61" s="4"/>
       <c r="N61" s="5"/>
     </row>
-    <row r="62" spans="1:14" customHeight="1" ht="64">
+    <row r="62" spans="1:14" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>35</v>
       </c>
@@ -5149,7 +5174,7 @@
       <c r="M62" s="4"/>
       <c r="N62" s="5"/>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -5165,7 +5190,7 @@
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -5181,7 +5206,7 @@
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -5197,7 +5222,7 @@
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -5213,7 +5238,7 @@
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -5229,7 +5254,7 @@
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -5245,7 +5270,7 @@
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -5261,7 +5286,7 @@
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -5277,7 +5302,7 @@
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -5293,7 +5318,7 @@
       <c r="M71" s="5"/>
       <c r="N71" s="5"/>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -5309,7 +5334,7 @@
       <c r="M72" s="5"/>
       <c r="N72" s="5"/>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -5325,7 +5350,7 @@
       <c r="M73" s="5"/>
       <c r="N73" s="5"/>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -5341,7 +5366,7 @@
       <c r="M74" s="5"/>
       <c r="N74" s="5"/>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -5357,7 +5382,7 @@
       <c r="M75" s="5"/>
       <c r="N75" s="5"/>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -5373,7 +5398,7 @@
       <c r="M76" s="5"/>
       <c r="N76" s="5"/>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -5389,7 +5414,7 @@
       <c r="M77" s="5"/>
       <c r="N77" s="5"/>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -5405,7 +5430,7 @@
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -5421,7 +5446,7 @@
       <c r="M79" s="5"/>
       <c r="N79" s="5"/>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -5437,7 +5462,7 @@
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -5453,7 +5478,7 @@
       <c r="M81" s="5"/>
       <c r="N81" s="5"/>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -5469,7 +5494,7 @@
       <c r="M82" s="5"/>
       <c r="N82" s="5"/>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -5485,7 +5510,7 @@
       <c r="M83" s="5"/>
       <c r="N83" s="5"/>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -5501,7 +5526,7 @@
       <c r="M84" s="5"/>
       <c r="N84" s="5"/>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -5517,7 +5542,7 @@
       <c r="M85" s="5"/>
       <c r="N85" s="5"/>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -5533,7 +5558,7 @@
       <c r="M86" s="5"/>
       <c r="N86" s="5"/>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -5549,7 +5574,7 @@
       <c r="M87" s="5"/>
       <c r="N87" s="5"/>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -5565,7 +5590,7 @@
       <c r="M88" s="5"/>
       <c r="N88" s="5"/>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -5581,7 +5606,7 @@
       <c r="M89" s="5"/>
       <c r="N89" s="5"/>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -5597,7 +5622,7 @@
       <c r="M90" s="5"/>
       <c r="N90" s="5"/>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -5613,7 +5638,7 @@
       <c r="M91" s="5"/>
       <c r="N91" s="5"/>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -5629,7 +5654,7 @@
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -5645,7 +5670,7 @@
       <c r="M93" s="5"/>
       <c r="N93" s="5"/>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -5661,7 +5686,7 @@
       <c r="M94" s="5"/>
       <c r="N94" s="5"/>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -5677,7 +5702,7 @@
       <c r="M95" s="5"/>
       <c r="N95" s="5"/>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -5693,7 +5718,7 @@
       <c r="M96" s="5"/>
       <c r="N96" s="5"/>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -5709,7 +5734,7 @@
       <c r="M97" s="5"/>
       <c r="N97" s="5"/>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -5725,7 +5750,7 @@
       <c r="M98" s="5"/>
       <c r="N98" s="5"/>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -5741,7 +5766,7 @@
       <c r="M99" s="5"/>
       <c r="N99" s="5"/>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -5757,7 +5782,7 @@
       <c r="M100" s="5"/>
       <c r="N100" s="5"/>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -5773,7 +5798,7 @@
       <c r="M101" s="5"/>
       <c r="N101" s="5"/>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -5789,7 +5814,7 @@
       <c r="M102" s="5"/>
       <c r="N102" s="5"/>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -5805,7 +5830,7 @@
       <c r="M103" s="5"/>
       <c r="N103" s="5"/>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -5821,7 +5846,7 @@
       <c r="M104" s="5"/>
       <c r="N104" s="5"/>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -5837,7 +5862,7 @@
       <c r="M105" s="5"/>
       <c r="N105" s="5"/>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -5853,7 +5878,7 @@
       <c r="M106" s="5"/>
       <c r="N106" s="5"/>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -5869,7 +5894,7 @@
       <c r="M107" s="5"/>
       <c r="N107" s="5"/>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -5885,7 +5910,7 @@
       <c r="M108" s="5"/>
       <c r="N108" s="5"/>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -5901,7 +5926,7 @@
       <c r="M109" s="5"/>
       <c r="N109" s="5"/>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -5917,7 +5942,7 @@
       <c r="M110" s="5"/>
       <c r="N110" s="5"/>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -5933,7 +5958,7 @@
       <c r="M111" s="5"/>
       <c r="N111" s="5"/>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -5949,7 +5974,7 @@
       <c r="M112" s="5"/>
       <c r="N112" s="5"/>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -5965,7 +5990,7 @@
       <c r="M113" s="5"/>
       <c r="N113" s="5"/>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -5981,7 +6006,7 @@
       <c r="M114" s="5"/>
       <c r="N114" s="5"/>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -5997,7 +6022,7 @@
       <c r="M115" s="5"/>
       <c r="N115" s="5"/>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -6013,7 +6038,7 @@
       <c r="M116" s="5"/>
       <c r="N116" s="5"/>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -6029,7 +6054,7 @@
       <c r="M117" s="5"/>
       <c r="N117" s="5"/>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -6045,7 +6070,7 @@
       <c r="M118" s="5"/>
       <c r="N118" s="5"/>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -6061,7 +6086,7 @@
       <c r="M119" s="5"/>
       <c r="N119" s="5"/>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -6077,7 +6102,7 @@
       <c r="M120" s="5"/>
       <c r="N120" s="5"/>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -6093,7 +6118,7 @@
       <c r="M121" s="5"/>
       <c r="N121" s="5"/>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -6109,7 +6134,7 @@
       <c r="M122" s="5"/>
       <c r="N122" s="5"/>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -6125,7 +6150,7 @@
       <c r="M123" s="5"/>
       <c r="N123" s="5"/>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -6141,7 +6166,7 @@
       <c r="M124" s="5"/>
       <c r="N124" s="5"/>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -6157,7 +6182,7 @@
       <c r="M125" s="5"/>
       <c r="N125" s="5"/>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -6173,7 +6198,7 @@
       <c r="M126" s="5"/>
       <c r="N126" s="5"/>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -6189,7 +6214,7 @@
       <c r="M127" s="5"/>
       <c r="N127" s="5"/>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -6205,7 +6230,7 @@
       <c r="M128" s="5"/>
       <c r="N128" s="5"/>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -6221,7 +6246,7 @@
       <c r="M129" s="5"/>
       <c r="N129" s="5"/>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -6237,7 +6262,7 @@
       <c r="M130" s="5"/>
       <c r="N130" s="5"/>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -6253,7 +6278,7 @@
       <c r="M131" s="5"/>
       <c r="N131" s="5"/>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -6269,7 +6294,7 @@
       <c r="M132" s="5"/>
       <c r="N132" s="5"/>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -6285,7 +6310,7 @@
       <c r="M133" s="5"/>
       <c r="N133" s="5"/>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -6301,7 +6326,7 @@
       <c r="M134" s="5"/>
       <c r="N134" s="5"/>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -6317,7 +6342,7 @@
       <c r="M135" s="5"/>
       <c r="N135" s="5"/>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -6333,7 +6358,7 @@
       <c r="M136" s="5"/>
       <c r="N136" s="5"/>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -6349,7 +6374,7 @@
       <c r="M137" s="5"/>
       <c r="N137" s="5"/>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -6365,7 +6390,7 @@
       <c r="M138" s="5"/>
       <c r="N138" s="5"/>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -6381,7 +6406,7 @@
       <c r="M139" s="5"/>
       <c r="N139" s="5"/>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -6398,7 +6423,7 @@
       <c r="N140" s="5"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="12">
     <mergeCell ref="I6:M6"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:M1"/>
@@ -6413,75 +6438,63 @@
     <mergeCell ref="J5:M5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D1" r:id="rId_hyperlink_1"/>
-    <hyperlink ref="E1" r:id="rId_hyperlink_2"/>
-    <hyperlink ref="F1" r:id="rId_hyperlink_3"/>
-    <hyperlink ref="G1" r:id="rId_hyperlink_4"/>
-    <hyperlink ref="H1" r:id="rId_hyperlink_5"/>
-    <hyperlink ref="I1" r:id="rId_hyperlink_6"/>
-    <hyperlink ref="J1" r:id="rId_hyperlink_7"/>
-    <hyperlink ref="K1" r:id="rId_hyperlink_8"/>
-    <hyperlink ref="L1" r:id="rId_hyperlink_9"/>
-    <hyperlink ref="M1" r:id="rId_hyperlink_10"/>
+    <hyperlink ref="D1" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E1" r:id="rId2" display="https://dev.azure.com/Styabudi/Local Internship/_sprints/taskboard/Local Internship Team/Local Internship/Sprint 1 Exercise BA" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="F1" r:id="rId3" display="https://dev.azure.com/Styabudi/Local Internship/_sprints/taskboard/Local Internship Team/Local Internship/Sprint 1 Exercise BA" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="G1" r:id="rId4" display="https://dev.azure.com/Styabudi/Local Internship/_sprints/taskboard/Local Internship Team/Local Internship/Sprint 1 Exercise BA" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="H1" r:id="rId5" display="https://dev.azure.com/Styabudi/Local Internship/_sprints/taskboard/Local Internship Team/Local Internship/Sprint 1 Exercise BA" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="I1" r:id="rId6" display="https://dev.azure.com/Styabudi/Local Internship/_sprints/taskboard/Local Internship Team/Local Internship/Sprint 1 Exercise BA" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="J1" r:id="rId7" display="https://dev.azure.com/Styabudi/Local Internship/_sprints/taskboard/Local Internship Team/Local Internship/Sprint 1 Exercise BA" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="K1" r:id="rId8" display="https://dev.azure.com/Styabudi/Local Internship/_sprints/taskboard/Local Internship Team/Local Internship/Sprint 1 Exercise BA" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="L1" r:id="rId9" display="https://dev.azure.com/Styabudi/Local Internship/_sprints/taskboard/Local Internship Team/Local Internship/Sprint 1 Exercise BA" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="M1" r:id="rId10" display="https://dev.azure.com/Styabudi/Local Internship/_sprints/taskboard/Local Internship Team/Local Internship/Sprint 1 Exercise BA" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
   </hyperlinks>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:C80"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="true" style="1"/>
-    <col min="2" max="2" width="56" customWidth="true" style="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="true" style="1"/>
+    <col min="1" max="1" width="30" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="37"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="22"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
     </row>
-    <row r="5" spans="1:3" customHeight="1" ht="20.4">
-      <c r="A5" s="42" t="s">
+    <row r="5" spans="1:3" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="57" t="s">
         <v>322</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="15"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="38" t="s">
+      <c r="B5" s="57"/>
+      <c r="C5" s="13"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
         <v>323</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -6489,8 +6502,8 @@
       </c>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="38" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="23" t="s">
         <v>324</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -6498,26 +6511,26 @@
       </c>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="38" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="24" t="s">
         <v>327</v>
       </c>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="38" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="54" t="s">
         <v>329</v>
       </c>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="38" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="23" t="s">
         <v>330</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -6525,53 +6538,53 @@
       </c>
       <c r="C10" s="5"/>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="38" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="23" t="s">
         <v>332</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="25" t="s">
         <v>333</v>
       </c>
       <c r="C11" s="5"/>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="38" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
         <v>334</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="54" t="s">
         <v>335</v>
       </c>
       <c r="C12" s="5"/>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="38" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="25" t="s">
         <v>337</v>
       </c>
       <c r="C13" s="5"/>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="38" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="54" t="s">
         <v>339</v>
       </c>
       <c r="C14" s="5"/>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
         <v>340</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="25" t="s">
         <v>337</v>
       </c>
       <c r="C15" s="5"/>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="38" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="23" t="s">
         <v>341</v>
       </c>
       <c r="B16" s="7" t="s">
@@ -6579,8 +6592,8 @@
       </c>
       <c r="C16" s="5"/>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="38" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
         <v>343</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -6588,17 +6601,17 @@
       </c>
       <c r="C17" s="5"/>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="38" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="26" t="s">
         <v>346</v>
       </c>
       <c r="C18" s="5"/>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="38" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="23" t="s">
         <v>347</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -6606,8 +6619,8 @@
       </c>
       <c r="C19" s="5"/>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="38" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="23" t="s">
         <v>349</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -6615,8 +6628,8 @@
       </c>
       <c r="C20" s="5"/>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="38" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
         <v>351</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -6624,8 +6637,8 @@
       </c>
       <c r="C21" s="5"/>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="38" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="23" t="s">
         <v>353</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -6633,8 +6646,8 @@
       </c>
       <c r="C22" s="5"/>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="38" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
         <v>355</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -6642,8 +6655,8 @@
       </c>
       <c r="C23" s="5"/>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="38" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="23" t="s">
         <v>356</v>
       </c>
       <c r="B24" s="4">
@@ -6651,8 +6664,8 @@
       </c>
       <c r="C24" s="5"/>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="38" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="23" t="s">
         <v>357</v>
       </c>
       <c r="B25" s="4">
@@ -6660,8 +6673,8 @@
       </c>
       <c r="C25" s="5"/>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="38" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="23" t="s">
         <v>358</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -6669,8 +6682,8 @@
       </c>
       <c r="C26" s="5"/>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="38" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="23" t="s">
         <v>320</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -6678,8 +6691,8 @@
       </c>
       <c r="C27" s="5"/>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="38" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="23" t="s">
         <v>361</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -6687,8 +6700,8 @@
       </c>
       <c r="C28" s="5"/>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="38" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="23" t="s">
         <v>363</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -6696,8 +6709,8 @@
       </c>
       <c r="C29" s="5"/>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="38" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="23" t="s">
         <v>365</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -6705,8 +6718,8 @@
       </c>
       <c r="C30" s="5"/>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="38" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="23" t="s">
         <v>366</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -6714,8 +6727,8 @@
       </c>
       <c r="C31" s="5"/>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="38" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="23" t="s">
         <v>367</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -6723,8 +6736,8 @@
       </c>
       <c r="C32" s="5"/>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="38" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="23" t="s">
         <v>369</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -6732,8 +6745,8 @@
       </c>
       <c r="C33" s="5"/>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="38" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="23" t="s">
         <v>370</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -6741,8 +6754,8 @@
       </c>
       <c r="C34" s="5"/>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="38" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="23" t="s">
         <v>372</v>
       </c>
       <c r="B35" s="4">
@@ -6750,8 +6763,8 @@
       </c>
       <c r="C35" s="5"/>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="38" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="23" t="s">
         <v>373</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -6759,8 +6772,8 @@
       </c>
       <c r="C36" s="5"/>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="38" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="23" t="s">
         <v>375</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -6768,8 +6781,8 @@
       </c>
       <c r="C37" s="5"/>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="38" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="23" t="s">
         <v>376</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -6777,295 +6790,283 @@
       </c>
       <c r="C38" s="5"/>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A5:B5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B9" r:id="rId_hyperlink_1"/>
-    <hyperlink ref="B11" r:id="rId_hyperlink_2"/>
-    <hyperlink ref="B13" r:id="rId_hyperlink_3"/>
-    <hyperlink ref="B15" r:id="rId_hyperlink_4"/>
+    <hyperlink ref="B9" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="B11" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="B13" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="B15" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="B12" r:id="rId5" xr:uid="{E2337E89-7EFA-4637-AB41-95A0C10F979B}"/>
+    <hyperlink ref="B14" r:id="rId6" xr:uid="{6217302D-260E-4360-8095-2B29B98C4E15}"/>
   </hyperlinks>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:J80"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="true" style="0"/>
-    <col min="2" max="2" width="34" customWidth="true" style="0"/>
-    <col min="3" max="3" width="44" customWidth="true" style="0"/>
-    <col min="4" max="4" width="13" customWidth="true" style="0"/>
-    <col min="5" max="5" width="13" customWidth="true" style="0"/>
-    <col min="6" max="6" width="12" customWidth="true" style="0"/>
-    <col min="7" max="7" width="16" customWidth="true" style="0"/>
-    <col min="8" max="8" width="38" customWidth="true" style="0"/>
-    <col min="9" max="9" width="38" customWidth="true" style="0"/>
-    <col min="10" max="10" width="16" customWidth="true" style="0"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="9" width="38" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="27" t="s">
         <v>379</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="27" t="s">
         <v>380</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="27" t="s">
         <v>381</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="27" t="s">
         <v>382</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="27" t="s">
         <v>383</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="42" t="s">
+      <c r="I1" s="27" t="s">
         <v>385</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:10" customHeight="1" ht="50">
+    <row r="2" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>386</v>
       </c>
@@ -7097,7 +7098,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="3" spans="1:10" customHeight="1" ht="50">
+    <row r="3" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -7109,7 +7110,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" customHeight="1" ht="50">
+    <row r="4" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -7121,7 +7122,7 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" customHeight="1" ht="50">
+    <row r="5" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -7133,7 +7134,7 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" customHeight="1" ht="50">
+    <row r="6" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -7145,7 +7146,7 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" customHeight="1" ht="50">
+    <row r="7" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -7157,7 +7158,7 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" customHeight="1" ht="50">
+    <row r="8" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -7169,1106 +7170,1093 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="15"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="15"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="15"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="15"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="15"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="15"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="15"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="15"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" s="15"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" s="15"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="15"/>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" s="15"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" s="15"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="15"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="15"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="15"/>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="15"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-    </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="15"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-    </row>
-    <row r="63" spans="1:10">
-      <c r="A63" s="15"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
-    </row>
-    <row r="64" spans="1:10">
-      <c r="A64" s="15"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15"/>
-    </row>
-    <row r="65" spans="1:10">
-      <c r="A65" s="15"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
-    </row>
-    <row r="66" spans="1:10">
-      <c r="A66" s="15"/>
-      <c r="B66" s="15"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="15"/>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" s="15"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" s="15"/>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" s="15"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
-    </row>
-    <row r="70" spans="1:10">
-      <c r="A70" s="15"/>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
-    </row>
-    <row r="71" spans="1:10">
-      <c r="A71" s="15"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-    </row>
-    <row r="72" spans="1:10">
-      <c r="A72" s="15"/>
-      <c r="B72" s="15"/>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="15"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="15"/>
-    </row>
-    <row r="73" spans="1:10">
-      <c r="A73" s="15"/>
-      <c r="B73" s="15"/>
-      <c r="C73" s="15"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="15"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="15"/>
-    </row>
-    <row r="74" spans="1:10">
-      <c r="A74" s="15"/>
-      <c r="B74" s="15"/>
-      <c r="C74" s="15"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="15"/>
-      <c r="I74" s="15"/>
-      <c r="J74" s="15"/>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" s="15"/>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
-      <c r="H75" s="15"/>
-      <c r="I75" s="15"/>
-      <c r="J75" s="15"/>
-    </row>
-    <row r="76" spans="1:10">
-      <c r="A76" s="15"/>
-      <c r="B76" s="15"/>
-      <c r="C76" s="15"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
-      <c r="I76" s="15"/>
-      <c r="J76" s="15"/>
-    </row>
-    <row r="77" spans="1:10">
-      <c r="A77" s="15"/>
-      <c r="B77" s="15"/>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
-    </row>
-    <row r="78" spans="1:10">
-      <c r="A78" s="15"/>
-      <c r="B78" s="15"/>
-      <c r="C78" s="15"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
-      <c r="H78" s="15"/>
-      <c r="I78" s="15"/>
-      <c r="J78" s="15"/>
-    </row>
-    <row r="79" spans="1:10">
-      <c r="A79" s="15"/>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
-      <c r="H79" s="15"/>
-      <c r="I79" s="15"/>
-      <c r="J79" s="15"/>
-    </row>
-    <row r="80" spans="1:10">
-      <c r="A80" s="15"/>
-      <c r="B80" s="15"/>
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
-      <c r="I80" s="15"/>
-      <c r="J80" s="15"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="13"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="13"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="13"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="13"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="13"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="13"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="13"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="13"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="13"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="13"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="13"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="13"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="13"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="13"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="13"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="13"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="13"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="13"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="13"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="13"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="13"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="13"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="13"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="13"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="13"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="13"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="13"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="13"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="13"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="13"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="13"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="13"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2F5396"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:I50"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="true" style="0"/>
-    <col min="2" max="2" width="30" customWidth="true" style="0"/>
-    <col min="3" max="3" width="14" customWidth="true" style="0"/>
-    <col min="4" max="4" width="12" customWidth="true" style="0"/>
-    <col min="5" max="5" width="12" customWidth="true" style="0"/>
-    <col min="6" max="6" width="18" customWidth="true" style="0"/>
-    <col min="7" max="7" width="16" customWidth="true" style="0"/>
-    <col min="8" max="8" width="14" customWidth="true" style="0"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customHeight="1" ht="18">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="75" t="s">
         <v>391</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-    </row>
-    <row r="2" spans="1:9" customHeight="1" ht="18">
-      <c r="A2" s="53" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="75" t="s">
         <v>392</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="43" t="s">
+      <c r="B2" s="75"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55" t="s">
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39" t="s">
         <v>393</v>
       </c>
-      <c r="G4" s="54"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="43" t="s">
+      <c r="G4" s="38"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="35" t="s">
         <v>395</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="55" t="s">
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="39" t="s">
         <v>396</v>
       </c>
-      <c r="G5" s="51">
+      <c r="G5" s="35">
         <v>55</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="43" t="s">
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="28" t="s">
         <v>397</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="35" t="s">
         <v>398</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="43" t="s">
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="28" t="s">
         <v>399</v>
       </c>
-      <c r="G6" s="56" t="s">
+      <c r="G6" s="40" t="s">
         <v>400</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="43" t="s">
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="28" t="s">
         <v>401</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="43" t="s">
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="28" t="s">
         <v>402</v>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="41">
         <f>IF(A14=0,0,C14/A14)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="15"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="43" t="s">
+      <c r="H7" s="43"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="15"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="15"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="15"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="15"/>
-    </row>
-    <row r="12" spans="1:9" customHeight="1" ht="21">
-      <c r="A12" s="66" t="s">
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="13"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="13"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="13"/>
+    </row>
+    <row r="12" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="50" t="s">
         <v>403</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="15"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="42" t="s">
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="13"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="27" t="s">
         <v>404</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="60" t="s">
+      <c r="G13" s="44" t="s">
         <v>406</v>
       </c>
-      <c r="H13" s="60" t="s">
+      <c r="H13" s="44" t="s">
         <v>407</v>
       </c>
-      <c r="I13" s="15"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>55</v>
       </c>
@@ -8292,469 +8280,456 @@
         <f>COUNTIF('Test Case'!J8:J62,"Pending")</f>
         <v>55</v>
       </c>
-      <c r="G14" s="61">
+      <c r="G14" s="45">
         <f>IF(A14=0,0,B14/A14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="61">
+      <c r="H14" s="45">
         <f>IF(B14=0,0,C14/B14)</f>
-        <v>0.9047619047619</v>
-      </c>
-      <c r="I14" s="15"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-    </row>
-    <row r="16" spans="1:9" customHeight="1" ht="21">
-      <c r="A16" s="66"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="50"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="15"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="45" t="s">
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="13"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="30" t="s">
         <v>408</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="15"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="45"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="15"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-    </row>
-    <row r="22" spans="1:9" customHeight="1" ht="21">
-      <c r="A22" s="66"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="46"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="47"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="15"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="15"/>
-    </row>
-    <row r="26" spans="1:9" customHeight="1" ht="21">
-      <c r="A26" s="67"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="15"/>
-    </row>
-    <row r="27" spans="1:9" customHeight="1" ht="64.2">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-    </row>
-    <row r="29" spans="1:9" customHeight="1" ht="21">
-      <c r="A29" s="66"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="49"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="15"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="50"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="15"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="50"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="15"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="15"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="15"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="15"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="15"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="13"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="30"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="13"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+    </row>
+    <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="50"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="31"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="32"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="13"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="13"/>
+    </row>
+    <row r="26" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="51"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="13"/>
+    </row>
+    <row r="27" spans="1:9" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="76"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+    </row>
+    <row r="29" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="50"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="33"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="13"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="34"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="47"/>
+      <c r="I37" s="13"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="34"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="13"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="13"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="13"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="13"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="13"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="13"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A27:D27"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="true" style="1"/>
-    <col min="2" max="2" width="60" customWidth="true" style="1"/>
-    <col min="3" max="3" width="18" customWidth="true" style="1"/>
-    <col min="4" max="4" width="8.88671875" customWidth="true" style="1"/>
-    <col min="5" max="5" width="10.33203125" customWidth="true" style="1"/>
-    <col min="6" max="6" width="10.33203125" customWidth="true" style="1"/>
-    <col min="7" max="7" width="8.88671875" customWidth="true" style="1"/>
+    <col min="1" max="1" width="42" style="1" customWidth="1"/>
+    <col min="2" max="2" width="60" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="27" t="s">
         <v>409</v>
       </c>
       <c r="C1" s="4"/>
-      <c r="D1" s="69"/>
+      <c r="D1" s="53"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
     </row>
-    <row r="2" spans="1:7" customHeight="1" ht="62">
+    <row r="2" spans="1:7" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -8762,12 +8737,12 @@
         <v>410</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="1:7" customHeight="1" ht="62">
+      <c r="D2" s="53"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="1:7" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
@@ -8775,12 +8750,12 @@
         <v>411</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:7" customHeight="1" ht="62">
+      <c r="D3" s="53"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:7" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -8788,12 +8763,12 @@
         <v>412</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-    </row>
-    <row r="5" spans="1:7" customHeight="1" ht="62">
+      <c r="D4" s="53"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5" spans="1:7" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
@@ -8801,12 +8776,12 @@
         <v>413</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-    </row>
-    <row r="6" spans="1:7" customHeight="1" ht="62">
+      <c r="D5" s="53"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+    </row>
+    <row r="6" spans="1:7" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
@@ -8819,7 +8794,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:7" customHeight="1" ht="62">
+    <row r="7" spans="1:7" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
@@ -8832,7 +8807,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" spans="1:7" customHeight="1" ht="62">
+    <row r="8" spans="1:7" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>30</v>
       </c>
@@ -8845,7 +8820,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:7" customHeight="1" ht="62">
+    <row r="9" spans="1:7" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>33</v>
       </c>
@@ -8858,7 +8833,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="1:7" customHeight="1" ht="62">
+    <row r="10" spans="1:7" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>36</v>
       </c>
@@ -8866,47 +8841,47 @@
         <v>415</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-    </row>
-    <row r="11" spans="1:7" customHeight="1" ht="57.6">
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+    </row>
+    <row r="11" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-    </row>
-    <row r="12" spans="1:7" customHeight="1" ht="72">
-      <c r="A12" s="68" t="s">
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+    </row>
+    <row r="12" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="52" t="s">
         <v>416</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-    </row>
-    <row r="13" spans="1:7" customHeight="1" ht="100.8">
-      <c r="A13" s="68" t="s">
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+    </row>
+    <row r="13" spans="1:7" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="52" t="s">
         <v>417</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="52" t="s">
         <v>418</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-    </row>
-    <row r="14" spans="1:7" customHeight="1" ht="40.2">
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>419</v>
       </c>
@@ -8916,12 +8891,12 @@
       <c r="C14" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-    </row>
-    <row r="15" spans="1:7" customHeight="1" ht="28.8">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>422</v>
       </c>
@@ -8931,12 +8906,12 @@
       <c r="C15" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>427</v>
       </c>
@@ -8951,7 +8926,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -8960,7 +8935,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -8969,7 +8944,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -8978,7 +8953,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -8987,7 +8962,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -8996,7 +8971,7 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -9005,7 +8980,7 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -9014,7 +8989,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -9023,7 +8998,7 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -9032,7 +9007,7 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -9041,7 +9016,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -9050,7 +9025,7 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -9059,7 +9034,7 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -9068,7 +9043,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -9077,7 +9052,7 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -9086,7 +9061,7 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -9095,7 +9070,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -9104,7 +9079,7 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -9113,7 +9088,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -9122,7 +9097,7 @@
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -9131,7 +9106,7 @@
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -9140,7 +9115,7 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -9149,7 +9124,7 @@
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -9158,7 +9133,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -9168,17 +9143,6 @@
       <c r="G40" s="5"/>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>